--- a/Capítulo02/Capítulo02/VASSOURAS.xlsx
+++ b/Capítulo02/Capítulo02/VASSOURAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Publica\PROF RAUL\_2024 EXCEL FORMAÇÃO 08-01-2024\_AVANÇADO 1 e 2\Capítulo02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA35D92A-B0BB-4979-81BA-68DFAFE6F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{DA35D92A-B0BB-4979-81BA-68DFAFE6F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFAE359E-3383-45BE-A9DD-E0FD0C70A400}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTOQUE" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>DATA DE HOJE:</t>
   </si>
@@ -74,13 +74,50 @@
   </si>
   <si>
     <t>DIA DA SEMANA</t>
+  </si>
+  <si>
+    <t>funções</t>
+  </si>
+  <si>
+    <t>#=AGORA() - traz data e hora atual / qualquer enter ou clique duplo para atualizar</t>
+  </si>
+  <si>
+    <t>#=HOJE() - traz data atual</t>
+  </si>
+  <si>
+    <t>#=ESCOLHER(F5;"dom";"seg";"ter";"qua";"qui";"sex";sáb) - para definir o nome do dia</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">para trazer a hora atual: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ctrl+shift+;</t>
+    </r>
+  </si>
+  <si>
+    <t>#=TEXTO(F1;"mmmm") / TEXTO(F1;"dddd")  - para definir o nome do dia ou do mês</t>
+  </si>
+  <si>
+    <t>#=DIATRABALHO.INTL(B8-1;1;1;FERIADOS!A:A) - definir o dia útil a partir do 1º dia do mês</t>
+  </si>
+  <si>
+    <t>#=DIATRABALHO.INTL(A11;1;1;FERIADOS!A:A) - definir os próximos dias úteis do mês</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,8 +148,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +167,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,21 +250,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -484,127 +597,226 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="411" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{F81ABE10-15BC-4567-A65E-D88233CD3AF1}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005502" version="1.0.0.13" store="WA200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;M4aC5MlF8oieix0V_rZ56&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="22" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="78.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="2">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="12">
         <f ca="1">TODAY()</f>
-        <v>45323</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+        <v>46293</v>
+      </c>
+      <c r="G1" s="14">
+        <v>0.82152777777777775</v>
+      </c>
+      <c r="H1" s="10">
+        <f ca="1">NOW()</f>
+        <v>46293.86745474537</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
       <c r="F2">
         <f ca="1">DAY(F1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
       <c r="F3">
         <f ca="1">MONTH(F1)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="17" t="str">
+        <f ca="1">TEXT(F1,"mmmm")</f>
+        <v>setembro</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4">
         <f ca="1">YEAR(F1)</f>
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+        <v>2026</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5">
         <f ca="1">WEEKDAY(F1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="17" t="str">
+        <f ca="1">TEXT(F1,"dddd")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K6" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="K7" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="23">
+        <v>43221</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="21">
+        <f>WORKDAY.INTL(B8-1,1,1,FERIADOS!A:A)</f>
+        <v>43222</v>
+      </c>
+      <c r="B11" s="25" t="str">
+        <f>TEXT(A11,"dddd")</f>
+        <v>quarta-feira</v>
+      </c>
       <c r="C11" s="4">
         <v>10</v>
       </c>
@@ -614,235 +826,466 @@
       <c r="E11" s="4">
         <v>15</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
+      <c r="F11" s="4">
+        <f>C11+D11-E11</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <f>WORKDAY.INTL(A11,1,1,FERIADOS!A:A)</f>
+        <v>43223</v>
+      </c>
+      <c r="B12" s="25" t="str">
+        <f t="shared" ref="B12:B30" si="0">TEXT(A12,"dddd")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="C12" s="4">
+        <f>F11</f>
+        <v>15</v>
+      </c>
       <c r="D12" s="4">
         <v>5</v>
       </c>
       <c r="E12" s="4">
         <v>20</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
+      <c r="F12" s="4">
+        <f t="shared" ref="F12:F30" si="1">C12+D12-E12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <f>WORKDAY.INTL(A12,1,1,FERIADOS!A:A)</f>
+        <v>43224</v>
+      </c>
+      <c r="B13" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="C13" s="4">
+        <f t="shared" ref="C13:C30" si="2">F12</f>
+        <v>0</v>
+      </c>
       <c r="D13" s="4">
         <v>10</v>
       </c>
       <c r="E13" s="4">
         <v>8</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <f>WORKDAY.INTL(A13,1,1,FERIADOS!A:A)</f>
+        <v>43227</v>
+      </c>
+      <c r="B14" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="C14" s="4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="D14" s="4">
         <v>23</v>
       </c>
       <c r="E14" s="4">
         <v>20</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
+      <c r="F14" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <f>WORKDAY.INTL(A14,1,1,FERIADOS!A:A)</f>
+        <v>43228</v>
+      </c>
+      <c r="B15" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="C15" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="D15" s="4">
         <v>25</v>
       </c>
       <c r="E15" s="4">
         <v>22</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
+      <c r="F15" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <f>WORKDAY.INTL(A15,1,1,FERIADOS!A:A)</f>
+        <v>43229</v>
+      </c>
+      <c r="B16" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quarta-feira</v>
+      </c>
+      <c r="C16" s="4">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="D16" s="4">
         <v>12</v>
       </c>
       <c r="E16" s="4">
         <v>10</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
+      <c r="A17" s="3">
+        <f>WORKDAY.INTL(A16,1,1,FERIADOS!A:A)</f>
+        <v>43230</v>
+      </c>
+      <c r="B17" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="C17" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
       <c r="D17" s="4">
         <v>20</v>
       </c>
       <c r="E17" s="4">
         <v>12</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
+      <c r="A18" s="3">
+        <f>WORKDAY.INTL(A17,1,1,FERIADOS!A:A)</f>
+        <v>43231</v>
+      </c>
+      <c r="B18" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="C18" s="4">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
       <c r="D18" s="4">
         <v>2</v>
       </c>
       <c r="E18" s="4">
         <v>15</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="3">
+        <f>WORKDAY.INTL(A18,1,1,FERIADOS!A:A)</f>
+        <v>43234</v>
+      </c>
+      <c r="B19" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="C19" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="D19" s="4">
         <v>13</v>
       </c>
       <c r="E19" s="4">
         <v>17</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
+      <c r="A20" s="3">
+        <f>WORKDAY.INTL(A19,1,1,FERIADOS!A:A)</f>
+        <v>43235</v>
+      </c>
+      <c r="B20" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="C20" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="D20" s="4">
         <v>20</v>
       </c>
       <c r="E20" s="4">
         <v>15</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="4">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="3">
+        <f>WORKDAY.INTL(A20,1,1,FERIADOS!A:A)</f>
+        <v>43236</v>
+      </c>
+      <c r="B21" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quarta-feira</v>
+      </c>
+      <c r="C21" s="4">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
       <c r="D21" s="4">
         <v>22</v>
       </c>
       <c r="E21" s="4">
         <v>25</v>
       </c>
-      <c r="F21" s="4"/>
+      <c r="F21" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
+      <c r="A22" s="3">
+        <f>WORKDAY.INTL(A21,1,1,FERIADOS!A:A)</f>
+        <v>43237</v>
+      </c>
+      <c r="B22" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="C22" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
       <c r="D22" s="4">
         <v>30</v>
       </c>
       <c r="E22" s="4">
         <v>24</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="3">
+        <f>WORKDAY.INTL(A22,1,1,FERIADOS!A:A)</f>
+        <v>43238</v>
+      </c>
+      <c r="B23" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="C23" s="4">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="D23" s="4">
         <v>45</v>
       </c>
       <c r="E23" s="4">
         <v>40</v>
       </c>
-      <c r="F23" s="4"/>
+      <c r="F23" s="4">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="3">
+        <f>WORKDAY.INTL(A23,1,1,FERIADOS!A:A)</f>
+        <v>43241</v>
+      </c>
+      <c r="B24" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="C24" s="4">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
       <c r="D24" s="4">
         <v>12</v>
       </c>
       <c r="E24" s="4">
         <v>25</v>
       </c>
-      <c r="F24" s="4"/>
+      <c r="F24" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="3">
+        <f>WORKDAY.INTL(A24,1,1,FERIADOS!A:A)</f>
+        <v>43242</v>
+      </c>
+      <c r="B25" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="C25" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="D25" s="4">
         <v>20</v>
       </c>
       <c r="E25" s="4">
         <v>10</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="4">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="3">
+        <f>WORKDAY.INTL(A25,1,1,FERIADOS!A:A)</f>
+        <v>43243</v>
+      </c>
+      <c r="B26" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quarta-feira</v>
+      </c>
+      <c r="C26" s="4">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="D26" s="4">
         <v>22</v>
       </c>
       <c r="E26" s="4">
         <v>25</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="3">
+        <f>WORKDAY.INTL(A26,1,1,FERIADOS!A:A)</f>
+        <v>43244</v>
+      </c>
+      <c r="B27" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="C27" s="4">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="D27" s="4">
         <v>25</v>
       </c>
       <c r="E27" s="4">
         <v>28</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="3">
+        <f>WORKDAY.INTL(A27,1,1,FERIADOS!A:A)</f>
+        <v>43245</v>
+      </c>
+      <c r="B28" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="C28" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="D28" s="4">
         <v>16</v>
       </c>
       <c r="E28" s="4">
         <v>21</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="3">
+        <f>WORKDAY.INTL(A28,1,1,FERIADOS!A:A)</f>
+        <v>43248</v>
+      </c>
+      <c r="B29" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="C29" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="D29" s="4">
         <v>35</v>
       </c>
       <c r="E29" s="4">
         <v>28</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
+      <c r="A30" s="3">
+        <f>WORKDAY.INTL(A29,1,1,FERIADOS!A:A)</f>
+        <v>43249</v>
+      </c>
+      <c r="B30" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="C30" s="4">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="D30" s="4">
         <v>13</v>
       </c>
       <c r="E30" s="4">
         <v>15</v>
       </c>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -890,21 +1333,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -1018,10 +1446,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CFB214D-FD1A-4A5B-9F34-160CCF196FF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FF61029-5113-4A13-9AD4-40A717D0DF70}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
@@ -1036,5 +1486,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FF61029-5113-4A13-9AD4-40A717D0DF70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CFB214D-FD1A-4A5B-9F34-160CCF196FF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>